--- a/branches/fix/translation-notice-highlight/StructureDefinition-preview-model.xlsx
+++ b/branches/fix/translation-notice-highlight/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T07:30:14+00:00</t>
+    <t>2026-09-10T18:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
